--- a/Assets/model/AnimationData.xlsx
+++ b/Assets/model/AnimationData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE3A17\就職関係\作品\Assets\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3950311F-C4C9-4FBB-9CAB-141D8B6EEF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2763E087-FE72-4CAF-A4D0-0E8753869B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>WOLK</t>
+    <t>WALK</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>

--- a/Assets/model/AnimationData.xlsx
+++ b/Assets/model/AnimationData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE3A17\就職関係\作品\Assets\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2763E087-FE72-4CAF-A4D0-0E8753869B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B192801-7C9A-49A7-8F81-0C2461B16B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29280" yWindow="480" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,11 +28,9 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>IDLE</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>WALK</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -368,7 +366,7 @@
         <v>0</v>
       </c>
       <c r="C1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D1">
         <v>1</v>
